--- a/data/credit_bond_2026-10-29.xlsx
+++ b/data/credit_bond_2026-10-29.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/1.5850</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -924,7 +924,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>032680610.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -963,7 +967,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9400</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1003,7 +1007,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -1131,7 +1139,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-10-29.xlsx
+++ b/data/credit_bond_2026-10-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-29" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-30" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-29</t>
+          <t>数据来源：DM    2026-10-30</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 24.96</t>
+          <t>C- 24.15</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1000,8 +1000,12 @@
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>7+</t>

--- a/data/credit_bond_2026-10-29.xlsx
+++ b/data/credit_bond_2026-10-29.xlsx
@@ -692,64 +692,72 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行三农债02</t>
+          <t>26铜梁金龙PPN002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>10-29 16:00</t>
-        </is>
-      </c>
-      <c r="C3" s="3"/>
+          <t>10-29 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>032680610.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>67.03</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行三农债01</t>
+          <t>26铜梁金龙PPN001</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.83Y</t>
+          <t>4.98Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.5984</t>
+          <t>1.9802</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.6100/1.5850</t>
+          <t>--/1.9400</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>重庆市铜梁区金龙城市建设发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 48.62</t>
+          <t>C- 24.15</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -759,12 +767,12 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 14:00</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -772,47 +780,47 @@
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>重庆市-铜梁区</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金全部专项用于发放涉农贷款，支持乡村振兴业务发展。</t>
+          <t>发行人本期定向债务融资工具基础发行规模人民币0.00亿元,发行金额上限人民币3.00亿元(含3.00亿元),募集资金用于偿还公司本部到期的债务融资工具本金。[25铜梁金龙PPN005]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,首创证券股份有限公司,东方证券股份有限公司,重庆银行股份有限公司,恒丰银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,重庆银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -827,70 +835,74 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年"三农"专项金融债券(第二期)</t>
+          <t>重庆市铜梁区金龙城市建设发展(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-11-02</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
+          <t>2031-11-02</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -911,73 +923,81 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26铜梁金龙PPN002</t>
+          <t>26重庆三峡银行三农债02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-29 18:00</t>
+          <t>10-29 16:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>032680610.IB</t>
+          <t>212680076.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>37.08</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26铜梁金龙PPN001</t>
+          <t>26重庆三峡银行三农债01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.98Y</t>
+          <t>2.83Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9802</t>
+          <t>1.5984</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/1.9400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>重庆市铜梁区金龙城市建设发展(集团)有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 24.15</t>
+          <t>B- 48.62</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -987,12 +1007,12 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-29 14:00</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1001,46 +1021,48 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>1.43</v>
-      </c>
+        <v>3.28</v>
+      </c>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>重庆市-铜梁区</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具基础发行规模人民币0.00亿元,发行金额上限人民币3.00亿元(含3.00亿元),募集资金用于偿还公司本部到期的债务融资工具本金。[25铜梁金龙PPN005]</t>
+          <t>本期债券的募集资金全部专项用于发放涉农贷款，支持乡村振兴业务发展。</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,重庆银行股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,首创证券股份有限公司,东方证券股份有限公司,重庆银行股份有限公司,恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1055,32 +1077,28 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>重庆市铜梁区金龙城市建设发展(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>重庆三峡银行股份有限公司2026年"三农"专项金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-11-02</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-11-02</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
@@ -1090,32 +1108,32 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1143,9 +1161,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
